--- a/artfynd/A 33088-2025 artfynd.xlsx
+++ b/artfynd/A 33088-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67535182</v>
+        <v>67535214</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533398.2871038945</v>
+        <v>533396</v>
       </c>
       <c r="R2" t="n">
-        <v>6334553.612030125</v>
+        <v>6334608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,19 +745,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67535212</v>
+        <v>67535237</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533395.6698652918</v>
+        <v>533379</v>
       </c>
       <c r="R3" t="n">
-        <v>6334608.374464421</v>
+        <v>6334552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,53 +885,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67535191</v>
+        <v>67535239</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gruvebo (500 m väster om), Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533398.2871038945</v>
+        <v>533401</v>
       </c>
       <c r="R4" t="n">
-        <v>6334553.612030125</v>
+        <v>6334559</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,27 +955,18 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1035,19 +990,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67535236</v>
+        <v>67535182</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1060,12 +1010,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533379.2749366415</v>
+        <v>533398</v>
       </c>
       <c r="R5" t="n">
-        <v>6334552.373339082</v>
+        <v>6334554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1060,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,37 +1095,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67535237</v>
+        <v>67535206</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533379.2749366415</v>
+        <v>533407</v>
       </c>
       <c r="R6" t="n">
-        <v>6334552.373339082</v>
+        <v>6334593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,19 +1165,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,19 +1200,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67535226</v>
+        <v>67535212</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1300,12 +1220,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533418.8228699055</v>
+        <v>533396</v>
       </c>
       <c r="R7" t="n">
-        <v>6334635.139874334</v>
+        <v>6334608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,19 +1270,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,19 +1305,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67535206</v>
+        <v>67535226</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1420,12 +1325,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533406.666190023</v>
+        <v>533419</v>
       </c>
       <c r="R8" t="n">
-        <v>6334592.733612346</v>
+        <v>6334635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,19 +1375,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,37 +1410,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67535214</v>
+        <v>67535235</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533395.6698652918</v>
+        <v>533379</v>
       </c>
       <c r="R9" t="n">
-        <v>6334608.374464421</v>
+        <v>6334552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,19 +1480,9 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-09-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67535239</v>
+        <v>67535191</v>
       </c>
       <c r="B10" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,36 +1526,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gruvebo (500 m väster om), Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533400.9604722789</v>
+        <v>533398</v>
       </c>
       <c r="R10" t="n">
-        <v>6334559.057825082</v>
+        <v>6334554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,28 +1586,17 @@
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-09-11</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
